--- a/2. Proyectos/1. Interpreta Chile/01 Meta - Proyectos/facebook scraper/data consolidado/facebook_candidatos_week_one_chile_13082025.xlsx
+++ b/2. Proyectos/1. Interpreta Chile/01 Meta - Proyectos/facebook scraper/data consolidado/facebook_candidatos_week_one_chile_13082025.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/josealonsoordinolaaucca/Documents/Documentos/Vault/Vault/2. Proyectos/1. Interpreta Chile/01 Meta - Proyectos/facebook scraper/data consolidado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037DDD17-CC04-C34F-B6BA-F9BA80E1BBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7018345C-93F9-B949-99F9-561AFD6CE7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="660" windowWidth="14160" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5374" uniqueCount="2154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5133" uniqueCount="2154">
   <si>
     <t>Usuario</t>
   </si>
@@ -6735,7 +6734,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6755,12 +6754,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -6815,16 +6808,13 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -7136,6 +7126,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -7157,7 +7148,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>2153</v>
       </c>
     </row>
@@ -31578,982 +31569,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{366E7A1F-B9C5-E841-B6EF-A2D6E1481820}">
-  <dimension ref="A1:B121"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>2040</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>2035</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>2058</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>2059</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>2060</v>
-      </c>
-      <c r="B6" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>2133</v>
-      </c>
-      <c r="B7" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>2119</v>
-      </c>
-      <c r="B8" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>2063</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>2055</v>
-      </c>
-      <c r="B10" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>2043</v>
-      </c>
-      <c r="B11" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>2053</v>
-      </c>
-      <c r="B12" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>2064</v>
-      </c>
-      <c r="B13" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>2097</v>
-      </c>
-      <c r="B14" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>2037</v>
-      </c>
-      <c r="B15" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>2031</v>
-      </c>
-      <c r="B16" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>2052</v>
-      </c>
-      <c r="B17" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>2050</v>
-      </c>
-      <c r="B18" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>2069</v>
-      </c>
-      <c r="B19" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>2095</v>
-      </c>
-      <c r="B20" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>2108</v>
-      </c>
-      <c r="B21" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>2032</v>
-      </c>
-      <c r="B22" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>2049</v>
-      </c>
-      <c r="B23" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>2036</v>
-      </c>
-      <c r="B24" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>2066</v>
-      </c>
-      <c r="B25" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>2086</v>
-      </c>
-      <c r="B26" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>2112</v>
-      </c>
-      <c r="B27" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>2082</v>
-      </c>
-      <c r="B28" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>2038</v>
-      </c>
-      <c r="B29" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>2092</v>
-      </c>
-      <c r="B30" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>2088</v>
-      </c>
-      <c r="B31" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>2106</v>
-      </c>
-      <c r="B32" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>2147</v>
-      </c>
-      <c r="B33" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>2128</v>
-      </c>
-      <c r="B34" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>2102</v>
-      </c>
-      <c r="B35" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>2074</v>
-      </c>
-      <c r="B36" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>2131</v>
-      </c>
-      <c r="B37" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>2113</v>
-      </c>
-      <c r="B38" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>2070</v>
-      </c>
-      <c r="B39" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>2033</v>
-      </c>
-      <c r="B40" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>2062</v>
-      </c>
-      <c r="B41" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>2100</v>
-      </c>
-      <c r="B42" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>2120</v>
-      </c>
-      <c r="B43" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>2090</v>
-      </c>
-      <c r="B44" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>2081</v>
-      </c>
-      <c r="B45" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>2041</v>
-      </c>
-      <c r="B46" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>2056</v>
-      </c>
-      <c r="B47" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>2107</v>
-      </c>
-      <c r="B48" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>2061</v>
-      </c>
-      <c r="B49" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>2093</v>
-      </c>
-      <c r="B50" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>2139</v>
-      </c>
-      <c r="B51" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>2071</v>
-      </c>
-      <c r="B52" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>2109</v>
-      </c>
-      <c r="B53" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>2103</v>
-      </c>
-      <c r="B54" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>2129</v>
-      </c>
-      <c r="B55" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>2125</v>
-      </c>
-      <c r="B56" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>2122</v>
-      </c>
-      <c r="B57" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>2042</v>
-      </c>
-      <c r="B58" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>2137</v>
-      </c>
-      <c r="B59" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>2127</v>
-      </c>
-      <c r="B60" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>2085</v>
-      </c>
-      <c r="B61" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>2083</v>
-      </c>
-      <c r="B62" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>2141</v>
-      </c>
-      <c r="B63" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>2146</v>
-      </c>
-      <c r="B64" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>2105</v>
-      </c>
-      <c r="B65" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>2078</v>
-      </c>
-      <c r="B66" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>2048</v>
-      </c>
-      <c r="B67" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>2143</v>
-      </c>
-      <c r="B68" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>2145</v>
-      </c>
-      <c r="B69" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>2124</v>
-      </c>
-      <c r="B70" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>2121</v>
-      </c>
-      <c r="B71" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>2140</v>
-      </c>
-      <c r="B72" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>2111</v>
-      </c>
-      <c r="B73" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>2110</v>
-      </c>
-      <c r="B74" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>2087</v>
-      </c>
-      <c r="B75" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>2072</v>
-      </c>
-      <c r="B76" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>2101</v>
-      </c>
-      <c r="B77" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>2080</v>
-      </c>
-      <c r="B78" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B79" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>2144</v>
-      </c>
-      <c r="B80" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>2135</v>
-      </c>
-      <c r="B81" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>2115</v>
-      </c>
-      <c r="B82" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>2132</v>
-      </c>
-      <c r="B83" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>2116</v>
-      </c>
-      <c r="B84" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>2136</v>
-      </c>
-      <c r="B85" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>2084</v>
-      </c>
-      <c r="B86" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>2123</v>
-      </c>
-      <c r="B87" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
-        <v>2130</v>
-      </c>
-      <c r="B88" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
-        <v>2039</v>
-      </c>
-      <c r="B89" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
-        <v>2104</v>
-      </c>
-      <c r="B90" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>2117</v>
-      </c>
-      <c r="B91" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>2094</v>
-      </c>
-      <c r="B92" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
-        <v>2118</v>
-      </c>
-      <c r="B93" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
-        <v>2046</v>
-      </c>
-      <c r="B94" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
-        <v>2148</v>
-      </c>
-      <c r="B95" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
-        <v>2138</v>
-      </c>
-      <c r="B96" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
-        <v>2126</v>
-      </c>
-      <c r="B97" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>2051</v>
-      </c>
-      <c r="B98" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
-        <v>2073</v>
-      </c>
-      <c r="B99" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
-        <v>2075</v>
-      </c>
-      <c r="B100" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>2096</v>
-      </c>
-      <c r="B101" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>2077</v>
-      </c>
-      <c r="B102" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
-        <v>2057</v>
-      </c>
-      <c r="B103" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
-        <v>2079</v>
-      </c>
-      <c r="B104" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
-        <v>2091</v>
-      </c>
-      <c r="B105" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
-        <v>2099</v>
-      </c>
-      <c r="B106" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
-        <v>2030</v>
-      </c>
-      <c r="B107" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A108" t="s">
-        <v>2044</v>
-      </c>
-      <c r="B108" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B109" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>2142</v>
-      </c>
-      <c r="B110" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
-        <v>2054</v>
-      </c>
-      <c r="B111" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
-        <v>2065</v>
-      </c>
-      <c r="B112" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
-        <v>2076</v>
-      </c>
-      <c r="B113" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>2089</v>
-      </c>
-      <c r="B114" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
-        <v>2134</v>
-      </c>
-      <c r="B115" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
-        <v>2098</v>
-      </c>
-      <c r="B116" t="s">
-        <v>2151</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
-        <v>2047</v>
-      </c>
-      <c r="B117" t="s">
-        <v>2151</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
-        <v>2029</v>
-      </c>
-      <c r="B118" t="s">
-        <v>2151</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
-        <v>2114</v>
-      </c>
-      <c r="B119" t="s">
-        <v>2151</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
-        <v>2034</v>
-      </c>
-      <c r="B120" t="s">
-        <v>2151</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
-        <v>2067</v>
-      </c>
-      <c r="B121" t="s">
-        <v>2151</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{21D40EF8-D1ED-B64B-8FB1-AE5A05A86865}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>